--- a/data/trans_dic/P1804_2016_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1804_2016_2023-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,12</t>
+          <t>4,87; 10,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,8</t>
+          <t>6,34; 11,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 17,43</t>
+          <t>9,58; 17,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 14,03</t>
+          <t>8,89; 14,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,36</t>
+          <t>7,93; 12,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,47</t>
+          <t>8,19; 11,89</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,44</t>
+          <t>2,78; 7,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 12,6</t>
+          <t>6,42; 13,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 14,8</t>
+          <t>7,26; 14,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 14,42</t>
+          <t>8,57; 14,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 9,69</t>
+          <t>5,66; 9,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,33</t>
+          <t>8,27; 12,5</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,69</t>
+          <t>4,36; 8,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 8,07</t>
+          <t>5,29; 10,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 17,86</t>
+          <t>7,53; 17,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 14,49</t>
+          <t>5,84; 15,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,91</t>
+          <t>5,85; 10,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,48</t>
+          <t>6,11; 10,85</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 8,49</t>
+          <t>5,55; 8,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,41</t>
+          <t>3,25; 5,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 12,56</t>
+          <t>8,15; 12,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,92</t>
+          <t>6,96; 10,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,88</t>
+          <t>7,08; 9,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,52</t>
+          <t>5,19; 7,43</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,93</t>
+          <t>4,06; 7,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,19</t>
+          <t>3,35; 8,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,96</t>
+          <t>7,68; 12,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,21</t>
+          <t>6,74; 10,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,58</t>
+          <t>6,58; 9,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,34</t>
+          <t>5,97; 8,69</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,0</t>
+          <t>3,45; 8,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,41</t>
+          <t>0,31; 4,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 10,53</t>
+          <t>6,64; 10,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,24</t>
+          <t>3,77; 6,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,35; 9,52</t>
+          <t>6,38; 9,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,13</t>
+          <t>3,29; 5,53</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,18</t>
+          <t>5,54; 7,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,58</t>
+          <t>5,34; 7,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,99; 11,03</t>
+          <t>8,89; 11,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,45</t>
+          <t>7,64; 9,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,9</t>
+          <t>7,53; 8,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,3</t>
+          <t>6,69; 8,01</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41327</t>
+          <t>48713</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49074</t>
+          <t>54535</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90402</t>
+          <t>103248</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20516; 43409</t>
+          <t>20909; 43321</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31106; 54548</t>
+          <t>34914; 65035</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34272; 60492</t>
+          <t>33243; 60556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39395; 62736</t>
+          <t>43197; 68538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58822; 95933</t>
+          <t>61517; 96558</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75277; 109286</t>
+          <t>84890; 123282</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40996</t>
+          <t>45011</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42048</t>
+          <t>47437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83044</t>
+          <t>92447</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10641; 28080</t>
+          <t>10506; 28070</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29022; 56964</t>
+          <t>31036; 63568</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27967; 55102</t>
+          <t>27032; 52316</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32786; 55156</t>
+          <t>36247; 61300</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42487; 72612</t>
+          <t>42434; 73948</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66868; 102937</t>
+          <t>74918; 113278</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45232</t>
+          <t>54022</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22622; 45375</t>
+          <t>22735; 45137</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10532; 53899</t>
+          <t>24944; 51603</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11980; 29664</t>
+          <t>12517; 29116</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9526; 24185</t>
+          <t>10957; 28410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39262; 68158</t>
+          <t>40259; 69566</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20427; 70821</t>
+          <t>40263; 71492</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42112</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62909</t>
+          <t>75307</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>105021</t>
+          <t>124570</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63714; 97630</t>
+          <t>63789; 98250</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30767; 55981</t>
+          <t>36733; 67785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67454; 103752</t>
+          <t>67347; 102997</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30065; 87228</t>
+          <t>59828; 90575</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>141489; 195265</t>
+          <t>139849; 189301</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76030; 131142</t>
+          <t>103368; 147883</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>30544</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>69639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90362</t>
+          <t>100183</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24632; 49203</t>
+          <t>25196; 48209</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17395; 43651</t>
+          <t>19025; 47726</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57925; 88306</t>
+          <t>56708; 89622</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44568; 77458</t>
+          <t>55991; 85606</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>88121; 130250</t>
+          <t>89371; 131164</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69676; 109851</t>
+          <t>83479; 121592</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36397</t>
+          <t>41182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40077</t>
+          <t>44961</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9126; 25845</t>
+          <t>9905; 25170</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>584; 13008</t>
+          <t>728; 11542</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72895; 113898</t>
+          <t>71863; 113426</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28191; 47331</t>
+          <t>31750; 52528</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86905; 130388</t>
+          <t>87366; 132828</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30600; 51280</t>
+          <t>35484; 59646</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>187080</t>
+          <t>213862</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>267056</t>
+          <t>305569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>454136</t>
+          <t>519431</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>188124; 243011</t>
+          <t>187712; 242939</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>143217; 222081</t>
+          <t>183858; 249448</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>317385; 389446</t>
+          <t>313927; 389572</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>218016; 301840</t>
+          <t>277064; 338050</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>521789; 615347</t>
+          <t>521037; 616061</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>393758; 507416</t>
+          <t>473049; 566256</t>
         </is>
       </c>
     </row>
